--- a/documentation/scrum/Product_Backlog.xlsx
+++ b/documentation/scrum/Product_Backlog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://micloud365-my.sharepoint.com/personal/imashai_millenniumitesp_com/Documents/Desktop/MSc BInA/Academics/3-Interactive Visualization/Assesment/Project/group4-interactive-visualisation/documentation/scrum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="11_EB55A1F75604DAD116EBA7F80FE7FDD3BE102FCF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{784F5183-0DDE-442F-B000-B20E7026CC76}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="11_EB55A1F75604DAD116EBA7F80FE7FDD3BE102FCF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A79577EC-41FF-40F4-861A-239A9F254F66}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Product Backlog" sheetId="1" r:id="rId1"/>
@@ -4561,8 +4561,8 @@
       <c r="E41" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="F41" s="19" t="s">
-        <v>239</v>
+      <c r="F41" s="20" t="s">
+        <v>241</v>
       </c>
       <c r="G41" s="18" t="s">
         <v>9</v>

--- a/documentation/scrum/Product_Backlog.xlsx
+++ b/documentation/scrum/Product_Backlog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://micloud365-my.sharepoint.com/personal/imashai_millenniumitesp_com/Documents/Desktop/MSc BInA/Academics/3-Interactive Visualization/Assesment/Project/group4-interactive-visualisation/documentation/scrum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="11_EB55A1F75604DAD116EBA7F80FE7FDD3BE102FCF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A79577EC-41FF-40F4-861A-239A9F254F66}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="11_EB55A1F75604DAD116EBA7F80FE7FDD3BE102FCF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31288C0A-9458-4354-8978-54696A639EF0}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Product Backlog" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,20 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Product Backlog'!$A$1:$E$107</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sprint Task Log'!$A$1:$G$95</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -4550,7 +4563,7 @@
         <v>303</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="C41" s="15" t="s">
         <v>305</v>
